--- a/DOSSIES_MULTIFORMATO/SSP/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SSP/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE01200</t>
+          <t>2020NE01202</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1064.35</v>
+        <v>16195.31</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anulação do saldo da 2020NE00438 no valor de R$ 1.064,35, conforme descrito no Memorando nº 062/2020-DOF/SSP de 28 de dezembro de 2020, em razão do encerramento do exercício/2020.</t>
+          <t>Anulação do saldo da 2020NE00919 no valor de R$ 16.195,31, conforme descrito no Memorando nº 062/2020-DOF/SSP, em razão do encerramento do exercício/2020.</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020NE01202</t>
+          <t>2020NE01200</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16195.31</v>
+        <v>1064.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anulação do saldo da 2020NE00919 no valor de R$ 16.195,31, conforme descrito no Memorando nº 062/2020-DOF/SSP, em razão do encerramento do exercício/2020.</t>
+          <t>Anulação do saldo da 2020NE00438 no valor de R$ 1.064,35, conforme descrito no Memorando nº 062/2020-DOF/SSP de 28 de dezembro de 2020, em razão do encerramento do exercício/2020.</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025NE0001172</t>
+          <t>2025NE0001171</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2025526.76</v>
+        <v>1487223.75</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025NE0001171</t>
+          <t>2025NE0001172</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1487223.75</v>
+        <v>2025526.76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025NE0002018</t>
+          <t>2025NE0002017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2025526.76</v>
+        <v>1487223.75</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025NE0002021</t>
+          <t>2025NE0002020</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>922698.8100000001</v>
+        <v>1509828.59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -879,14 +879,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anulação parcial da 2025NE0000887 no valor de R$ 922.698,81, conforme execução até 08/2025, nos termos do MEMORANDO Nº 142/2025-DOF/SSP-AM.</t>
+          <t>Anulação parcial da 2025NE0000885 no valor de R$ 1.509.828,59, conforme execução até 08/2025, nos termos do MEMORANDO Nº 142/2025-DOF/SSP-AM.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025NE0002020</t>
+          <t>2025NE0002021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1509828.59</v>
+        <v>922698.8100000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -905,14 +905,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anulação parcial da 2025NE0000885 no valor de R$ 1.509.828,59, conforme execução até 08/2025, nos termos do MEMORANDO Nº 142/2025-DOF/SSP-AM.</t>
+          <t>Anulação parcial da 2025NE0000887 no valor de R$ 922.698,81, conforme execução até 08/2025, nos termos do MEMORANDO Nº 142/2025-DOF/SSP-AM.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025NE0002017</t>
+          <t>2025NE0002018</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1487223.75</v>
+        <v>2025526.76</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2018NE01137</t>
+          <t>2018NE01140</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>211799.95</v>
+        <v>281919.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2018NE01142</t>
+          <t>2018NE01136</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>151828.48</v>
+        <v>945610.24</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2018NE01181</t>
+          <t>2018NE01145</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>48194.39</v>
+        <v>573839.36</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1069,14 +1069,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2018NE01139</t>
+          <t>2018NE01143</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>151738.93</v>
+        <v>151828.48</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2018NE01135</t>
+          <t>2018NE01141</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>509.09</v>
+        <v>151828.48</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2018NE01156</t>
+          <t>2018NE01150</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>303477.86</v>
+        <v>261005.89</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2018NE01148</t>
+          <t>2018NE01146</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2018NE01191</t>
+          <t>2018NE01153</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>358916.21</v>
+        <v>211799.95</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1199,14 +1199,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2018NE01134</t>
+          <t>2018NE01147</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>211781.19</v>
+        <v>1747120.16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2018NE01149</t>
+          <t>2018NE01144</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>261005.89</v>
+        <v>573839.36</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018NE01151</t>
+          <t>2018NE01138</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>423599.9</v>
+        <v>211781.19</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2018NE01155</t>
+          <t>2018NE01152</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>624634.3199999999</v>
+        <v>211799.95</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2018NE01152</t>
+          <t>2018NE01155</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>211799.95</v>
+        <v>624634.3199999999</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2018NE01138</t>
+          <t>2018NE01151</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>211781.19</v>
+        <v>423599.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2018NE01144</t>
+          <t>2018NE01149</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>573839.36</v>
+        <v>261005.89</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2018NE01147</t>
+          <t>2018NE01134</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1747120.16</v>
+        <v>211781.19</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2018NE01153</t>
+          <t>2018NE01191</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>211799.95</v>
+        <v>358916.21</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1459,14 +1459,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2018NE01146</t>
+          <t>2018NE01148</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2018NE01150</t>
+          <t>2018NE01156</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>261005.89</v>
+        <v>303477.86</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2018NE01141</t>
+          <t>2018NE01135</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>151828.48</v>
+        <v>509.09</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2018NE01143</t>
+          <t>2018NE01139</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>151828.48</v>
+        <v>151738.93</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018NE01145</t>
+          <t>2018NE01181</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>573839.36</v>
+        <v>48194.39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018NE01136</t>
+          <t>2018NE01142</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>945610.24</v>
+        <v>151828.48</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018NE01140</t>
+          <t>2018NE01137</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>281919.5</v>
+        <v>211799.95</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2023NE0000438</t>
+          <t>2023NE00438</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Contratação de empresa para serviço de acesso à internet, acesso a MetroMao, circuito de transmissão de dados, licença de sistema, hospedagem, Firewall, Datawarehouse, suporte técnico, desenvolvimento</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2023NE00438</t>
+          <t>2023NE0000438</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação de empresa para serviço de acesso à internet, acesso a MetroMao, circuito de transmissão de dados, licença de sistema, hospedagem, Firewall, Datawarehouse, suporte técnico, desenvolvimento</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024NE0001659</t>
+          <t>2024NE0001657</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15874.46</v>
+        <v>7411.51</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1757,14 +1757,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anulação do saldo remanescente da 2023NE0000003 no valor de R$ 15.874,46, conforme orientação contida no Decreto nº 50.522 de 22/10/2024 que trata do enceramento da execução orçamentária, financeira e</t>
+          <t xml:space="preserve">Anulação do saldo remanescente da 2023NE0000930 no valor de R$ 7.411,51, conforme orientação contida no Decreto nº 50.522 de 22/10/2024 que trata do enceramento da execução orçamentária, financeira e </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024NE0001657</t>
+          <t>2024NE0001659</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7411.51</v>
+        <v>15874.46</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anulação do saldo remanescente da 2023NE0000930 no valor de R$ 7.411,51, conforme orientação contida no Decreto nº 50.522 de 22/10/2024 que trata do enceramento da execução orçamentária, financeira e </t>
+          <t>Anulação do saldo remanescente da 2023NE0000003 no valor de R$ 15.874,46, conforme orientação contida no Decreto nº 50.522 de 22/10/2024 que trata do enceramento da execução orçamentária, financeira e</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2015NE00284</t>
+          <t>2015NE00285</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>94/2011</t>
+          <t>67/2012</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>172111.36</v>
+        <v>776531.03</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1839,19 +1839,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Despesa com reconhecimento de divida - Folha de Informação 046/2015 do Contratos 094/2011 ref. a prestação de serviços de implantação de solução tecnológica integrada de monitoramento, comando e contr</t>
+          <t>Despesa com reconhecimento de divida Folha de Informação 045/2015 do Contratos 067/2011 ref. a prestação de serviços de desenvolvimento e hospedagem de sistema de segurança pública.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2015NE00285</t>
+          <t>2015NE00284</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>67/2012</t>
+          <t>94/2011</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>776531.03</v>
+        <v>172111.36</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Despesa com reconhecimento de divida Folha de Informação 045/2015 do Contratos 067/2011 ref. a prestação de serviços de desenvolvimento e hospedagem de sistema de segurança pública.</t>
+          <t>Despesa com reconhecimento de divida - Folha de Informação 046/2015 do Contratos 094/2011 ref. a prestação de serviços de implantação de solução tecnológica integrada de monitoramento, comando e contr</t>
         </is>
       </c>
     </row>
@@ -1962,21 +1962,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2021NE0001415</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>48/2021</t>
-        </is>
-      </c>
+          <t>2021NE0001410</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>23/09/2021</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>535952.26</v>
+        <v>292828.26</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1985,24 +1981,28 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso à internet,desenvolvimento de sistema de informação,serviço de transmissão de dados, serviços de informática,hospedagem de sistema de informa</t>
+          <t>Anulação parcial da 2021NE0000991 no valor R$ 292.828,26, conforme descrito no Memorando 131/2021-DOF/SSP, Memorando Circular nº 018/2021-GSE/SSP e resposta do fiscal na folha 11 do Memorando Circular</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2021NE0001410</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>2021NE0001415</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>48/2021</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>23/09/2021</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>292828.26</v>
+        <v>535952.26</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anulação parcial da 2021NE0000991 no valor R$ 292.828,26, conforme descrito no Memorando 131/2021-DOF/SSP, Memorando Circular nº 018/2021-GSE/SSP e resposta do fiscal na folha 11 do Memorando Circular</t>
+          <t>Contratação de empresa especializada em serviços de acesso à internet,desenvolvimento de sistema de informação,serviço de transmissão de dados, serviços de informática,hospedagem de sistema de informa</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025NE0001952</t>
+          <t>2025NE0001953</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7617.78</v>
+        <v>5881.12</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025NE0001953</t>
+          <t>2025NE0001952</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5881.12</v>
+        <v>7617.78</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025NE0001639</t>
+          <t>2025NE0001638</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1487223.75</v>
+        <v>2025526.76</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025NE0001638</t>
+          <t>2025NE0001639</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2025526.76</v>
+        <v>1487223.75</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2021NE0000660</t>
+          <t>2021NE0000658</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>360021.56</v>
+        <v>500362.04</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2321,14 +2321,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Despesa com pagamento de prestação de serviço de internet. NFS-e Nºs 5029; 5030; 5033; 5035 e 5036, referente ao mês de nov/18; oriundo do TC 18/2016-SSP, para atender as necessidades do SSP. Parecer </t>
+          <t>Despesa com pgto. de prest. de serv. de internet, hospedagem de sistema e manut. de rede, conf. NFS-e Nºs: 5448; 5449; 5450; 5451; 5452; 5453; 5454 e 5455, ref. ao mês de dez/18; oriundo do TC 18/2016</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2021NE0000659</t>
+          <t>2021NE0000661</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>502299.07</v>
+        <v>296457.13</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2347,14 +2347,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Despesa com pgto de prest. de serviços de informática, NFS-e Nºs. 12196; 12197; 12198; 12199; 12200; 12201; 12202; 12203 e 12204, ref. ao mês de dez/19; oriundo do TC 18/2016-SSP. Parecer Nº 00243/202</t>
+          <t>Despesa com pgto de prestação de serviço de informática. NFS-e Nºs. 11658; 11660; 11661; 11663, ref. ao valor líquido (remanescente) do mês de nov/19; oriundo do TC 18/2016-SSP, para atender as necess</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2021NE0000661</t>
+          <t>2021NE0000659</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>296457.13</v>
+        <v>502299.07</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2373,14 +2373,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Despesa com pgto de prestação de serviço de informática. NFS-e Nºs. 11658; 11660; 11661; 11663, ref. ao valor líquido (remanescente) do mês de nov/19; oriundo do TC 18/2016-SSP, para atender as necess</t>
+          <t>Despesa com pgto de prest. de serviços de informática, NFS-e Nºs. 12196; 12197; 12198; 12199; 12200; 12201; 12202; 12203 e 12204, ref. ao mês de dez/19; oriundo do TC 18/2016-SSP. Parecer Nº 00243/202</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2021NE0000658</t>
+          <t>2021NE0000660</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>500362.04</v>
+        <v>360021.56</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Despesa com pgto. de prest. de serv. de internet, hospedagem de sistema e manut. de rede, conf. NFS-e Nºs: 5448; 5449; 5450; 5451; 5452; 5453; 5454 e 5455, ref. ao mês de dez/18; oriundo do TC 18/2016</t>
+          <t xml:space="preserve">Despesa com pagamento de prestação de serviço de internet. NFS-e Nºs 5029; 5030; 5033; 5035 e 5036, referente ao mês de nov/18; oriundo do TC 18/2016-SSP, para atender as necessidades do SSP. Parecer </t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025NE0001373</t>
+          <t>2025NE0001374</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1487223.75</v>
+        <v>2025526.76</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025NE0001374</t>
+          <t>2025NE0001373</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2025526.76</v>
+        <v>1487223.75</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2018NE00676</t>
+          <t>2018NE00662</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>83/2014</t>
+          <t>67/2012</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>261005.89</v>
+        <v>211799.95</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2661,19 +2661,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00153, REF. AO MÊS DE JULHO/2015 DO CONTRATO Nº 83/2014-SSP/AM.</t>
+          <t>Despesa para atender pagamento, objeto do serviço de informática prestado a Secretaria de Segurança.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2018NE00669</t>
+          <t>2018NE00674</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>94/2011</t>
+          <t>P.55/2015</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>151828.48</v>
+        <v>261005.89</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2691,19 +2691,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 15484, que corresponde ao mês de agosto/2015.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00218, REF. AO MÊS DE SETEMBRO/2015 DO CONTRATO Nº 55/2015-SSP/AM.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2018NE00660</t>
+          <t>2018NE00680</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>P.194/2016</t>
+          <t>18/2016</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>509.09</v>
+        <v>436780.04</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2721,19 +2721,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do serviço de informática prestado da SSP, referente a Nota Fiscal 20207, que corresponde ao mês de setembro/2016.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2018RD00136, REF. AO MÊS DE NOVEMBRO/2017.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2018NE00678</t>
+          <t>2018NE00675</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>P.54/2015</t>
+          <t>83/2014</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>211799.95</v>
+        <v>261005.89</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2751,19 +2751,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00151, REF. AO MÊS DE AGOSTO/2015.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00150, REF. AO MÊS DE AGOSTO/2015 DO CONTRATO Nº 083/2014-SSP/AM.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2018NE00665</t>
+          <t>2018NE00670</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>P.193/2015</t>
+          <t>68/2012</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>151738.93</v>
+        <v>573839.36</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2781,19 +2781,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento referente ao serviço de suporte técnico em Sistema de Informação Nota Fiscal 17138 que corresponde ao mês de dez/2015.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 068/2012-SSP, referente a Nota Fiscal 14231, que corresponde ao mês de abril/2015.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2018NE00679</t>
+          <t>2018NE00673</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>P.54/2015</t>
+          <t>P.22/2016</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>211799.95</v>
+        <v>1747120.16</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2811,19 +2811,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00151, REF. AO MÊS DE JULHO/2015.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2017RD00271, REF. AOS MESES DE JANEIRO/FEVEREIRO/MARÇO E ABRIL/2016.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2018NE00666</t>
+          <t>2018NE00661</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>94/2011</t>
+          <t>P.54/2015</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>281919.5</v>
+        <v>945610.24</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2841,19 +2841,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 14451, que corresponde ao mês de abril/2015.</t>
+          <t>Despesa para atender pagamento, objeto de serviço de informática prestado para Secretaria de Segurança, processo com várias notas fiscais e meses diversos todos anexo no mesmo.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2018NE00681</t>
+          <t>2018NE00671</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>P.54/2015</t>
+          <t>68/2012</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>624634.3199999999</v>
+        <v>573839.36</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2871,24 +2871,28 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2017RD00331, REF. AO MÊS DE JUNHO/2015.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 068/2012-SSP, referente a Nota Fiscal 13801, que corresponde ao mês de março/2015.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2018NE00682</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>2018NE00659</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>67/2012</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>17/07/2018</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>455216.79</v>
+        <v>211781.19</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2897,19 +2901,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 664/2018, PARA CORREÇÃO NO VALOR INFORMADO NA RD2017RD00273.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 067/2015-SSP, referente a Nota Fiscal 13800, que corresponde ao mês de março/2015.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2018NE00668</t>
+          <t>2018NE00663</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>94/2011</t>
+          <t>67/2012</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2918,7 +2922,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>151828.48</v>
+        <v>211781.19</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2927,19 +2931,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 15170, que corresponde ao mês de julho/2015.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 067/2015-SSP, referente a Nota Fiscal 14229, que corresponde ao mês de abril/2015.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2018NE00667</t>
+          <t>2018NE00677</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>94/2011</t>
+          <t>P.193/2015</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2948,7 +2952,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>151828.48</v>
+        <v>423599.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2957,19 +2961,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 14690, que corresponde ao mês de maio/2015.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00219, REF. AO MÊS DE SETEMBRO/2015 e DEZEMBRO/2015.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2018NE00672</t>
+          <t>2018NE00664</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>68/2012</t>
+          <t>94/2011</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2978,7 +2982,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>261005.89</v>
+        <v>455216.79</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2987,19 +2991,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 068/2012-SSP, referente as Notas Fiscal 14696, 14697, 14698, 14699 e 14700, que corresponde ao mês de maio/2015.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 16732, 16724 e 16980, que corresponde aos meses de out, nov e dez/2016.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2018NE00664</t>
+          <t>2018NE00672</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>94/2011</t>
+          <t>68/2012</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3008,7 +3012,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>455216.79</v>
+        <v>261005.89</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3017,19 +3021,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 16732, 16724 e 16980, que corresponde aos meses de out, nov e dez/2016.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 068/2012-SSP, referente as Notas Fiscal 14696, 14697, 14698, 14699 e 14700, que corresponde ao mês de maio/2015.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2018NE00677</t>
+          <t>2018NE00667</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>P.193/2015</t>
+          <t>94/2011</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3038,7 +3042,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>423599.9</v>
+        <v>151828.48</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3047,19 +3051,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00219, REF. AO MÊS DE SETEMBRO/2015 e DEZEMBRO/2015.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 14690, que corresponde ao mês de maio/2015.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2018NE00663</t>
+          <t>2018NE00668</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>67/2012</t>
+          <t>94/2011</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3068,7 +3072,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>211781.19</v>
+        <v>151828.48</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3077,28 +3081,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 067/2015-SSP, referente a Nota Fiscal 14229, que corresponde ao mês de abril/2015.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 15170, que corresponde ao mês de julho/2015.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2018NE00659</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>67/2012</t>
-        </is>
-      </c>
+          <t>2018NE00682</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>17/07/2018</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>211781.19</v>
+        <v>455216.79</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3107,19 +3107,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 067/2015-SSP, referente a Nota Fiscal 13800, que corresponde ao mês de março/2015.</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO Nº 664/2018, PARA CORREÇÃO NO VALOR INFORMADO NA RD2017RD00273.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2018NE00671</t>
+          <t>2018NE00681</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>68/2012</t>
+          <t>P.54/2015</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>573839.36</v>
+        <v>624634.3199999999</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3137,19 +3137,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 068/2012-SSP, referente a Nota Fiscal 13801, que corresponde ao mês de março/2015.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2017RD00331, REF. AO MÊS DE JUNHO/2015.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2018NE00661</t>
+          <t>2018NE00666</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>P.54/2015</t>
+          <t>94/2011</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>945610.24</v>
+        <v>281919.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3167,19 +3167,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto de serviço de informática prestado para Secretaria de Segurança, processo com várias notas fiscais e meses diversos todos anexo no mesmo.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 14451, que corresponde ao mês de abril/2015.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2018NE00673</t>
+          <t>2018NE00679</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>P.22/2016</t>
+          <t>P.54/2015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1747120.16</v>
+        <v>211799.95</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3197,19 +3197,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2017RD00271, REF. AOS MESES DE JANEIRO/FEVEREIRO/MARÇO E ABRIL/2016.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00151, REF. AO MÊS DE JULHO/2015.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2018NE00670</t>
+          <t>2018NE00665</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>68/2012</t>
+          <t>P.193/2015</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>573839.36</v>
+        <v>151738.93</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3227,19 +3227,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do Contrato nº 068/2012-SSP, referente a Nota Fiscal 14231, que corresponde ao mês de abril/2015.</t>
+          <t>Despesa para atender pagamento referente ao serviço de suporte técnico em Sistema de Informação Nota Fiscal 17138 que corresponde ao mês de dez/2015.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2018NE00675</t>
+          <t>2018NE00678</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>83/2014</t>
+          <t>P.54/2015</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>261005.89</v>
+        <v>211799.95</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3257,19 +3257,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00150, REF. AO MÊS DE AGOSTO/2015 DO CONTRATO Nº 083/2014-SSP/AM.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00151, REF. AO MÊS DE AGOSTO/2015.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2018NE00680</t>
+          <t>2018NE00660</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>18/2016</t>
+          <t>P.194/2016</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>436780.04</v>
+        <v>509.09</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3287,19 +3287,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2018RD00136, REF. AO MÊS DE NOVEMBRO/2017.</t>
+          <t>Despesa para atender pagamento, objeto do serviço de informática prestado da SSP, referente a Nota Fiscal 20207, que corresponde ao mês de setembro/2016.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2018NE00674</t>
+          <t>2018NE00669</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>P.55/2015</t>
+          <t>94/2011</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>261005.89</v>
+        <v>151828.48</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3317,19 +3317,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00218, REF. AO MÊS DE SETEMBRO/2015 DO CONTRATO Nº 55/2015-SSP/AM.</t>
+          <t>Despesa para atender pagamento, objeto do Contrato nº 94/2011-SSP, referente a Nota Fiscal 15484, que corresponde ao mês de agosto/2015.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2018NE00662</t>
+          <t>2018NE00676</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>67/2012</t>
+          <t>83/2014</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>211799.95</v>
+        <v>261005.89</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3347,14 +3347,14 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Despesa para atender pagamento, objeto do serviço de informática prestado a Secretaria de Segurança.</t>
+          <t>DESPESA COM PAGAMENTO DE RECONHECIMENTO DE DÍVIDA - 2016RD00153, REF. AO MÊS DE JULHO/2015 DO CONTRATO Nº 83/2014-SSP/AM.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020NE00807</t>
+          <t>2020NE00809</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>20222.69</v>
+        <v>22351.39</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3373,14 +3373,14 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Anulação parcial do saldo da 2020NE00438 no valor de R$ 20.222,69, conforme descrito no Memorando nº 006/2020-DETEC/SSP de 14 de outubro de 2020.</t>
+          <t>Anulação parcial do saldo da 2020NE00001 no valor de R$ 22.351,39, conforme descrito no Memorando nº 006/2020-DETEC/SSP de 14 de outubro de 2020.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020NE00809</t>
+          <t>2020NE00807</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>22351.39</v>
+        <v>20222.69</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Anulação parcial do saldo da 2020NE00001 no valor de R$ 22.351,39, conforme descrito no Memorando nº 006/2020-DETEC/SSP de 14 de outubro de 2020.</t>
+          <t>Anulação parcial do saldo da 2020NE00438 no valor de R$ 20.222,69, conforme descrito no Memorando nº 006/2020-DETEC/SSP de 14 de outubro de 2020.</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025NE0000887</t>
+          <t>2025NE0000885</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>945245.8199999999</v>
+        <v>694037.75</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025NE0000885</t>
+          <t>2025NE0000887</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>694037.75</v>
+        <v>945245.8199999999</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2023NE0001326</t>
+          <t>2023NE0001327</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>250111.05</v>
+        <v>214380.91</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2023NE0001327</t>
+          <t>2023NE0001326</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>214380.91</v>
+        <v>250111.05</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2021NE0000649</t>
+          <t>2021NE0000644</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>701234.12</v>
+        <v>945610.24</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>DESPESAS COM SERVIÇOS DE HOSPEDAGEM DE SISTEMAS DE SERVIDORES E OUTROS, NFS-e nºs: 16730, 16731, 16738, 16739, 16725, 16726, 16727, 16728, 16729, 16733, 16734, 16735, 16736, 16737 e PROPOSTA Nº 055/20</t>
+          <t>Anulação total da 2021NE0000609 no valor R$ 945.610,24 para ajuste no cronograma.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2021NE0000644</t>
+          <t>2021NE0000649</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>945610.24</v>
+        <v>701234.12</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Anulação total da 2021NE0000609 no valor R$ 945.610,24 para ajuste no cronograma.</t>
+          <t>DESPESAS COM SERVIÇOS DE HOSPEDAGEM DE SISTEMAS DE SERVIDORES E OUTROS, NFS-e nºs: 16730, 16731, 16738, 16739, 16725, 16726, 16727, 16728, 16729, 16733, 16734, 16735, 16736, 16737 e PROPOSTA Nº 055/20</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2016</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA PARA ATENDER NECESSIDADES DA SSP/AM.</t>
         </is>
       </c>
     </row>
@@ -3717,14 +3717,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA PARA ATENDER NECESSIDADES DA SSP/AM.</t>
+          <t>Cobertura Financeira 2016</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025NE0001887</t>
+          <t>2025NE0001888</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1487223.75</v>
+        <v>2025526.76</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025NE0001888</t>
+          <t>2025NE0001887</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2025526.76</v>
+        <v>1487223.75</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2021NE0000614</t>
+          <t>2021NE0000611</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>436780.04</v>
+        <v>151738.93</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3803,14 +3803,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Despesa de exercício anterior referente a prestação de serviço de Hospedagem de sistema e suporte técnico em sistema de informação, para atender as necessidades do SSP, NFS-e nº 25802, 25803, 25804, 2</t>
+          <t>DESPESAS COM SERVIÇOS DE SUPORTE TÉCNICO EM SISTEMAS DE INFORMAÇÃO, NFS-e Nº 17138 VALOR R$ 151.738,93, REFERENTE AO MÊS DE DEZEMBRO/2015, PARA ATENDER NECESSIDADES DO SISTEMA DE SEGURANÇA PUBLICA.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2021NE0000613</t>
+          <t>2021NE0000610</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1747120.16</v>
+        <v>303477.86</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3829,14 +3829,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Despesas com serviços de hospedagem de sistemas de servidores e outros; NFS-e 18092 a 18099; 18100 a 18107; 18109 a 18116; 18699 a 18706; referentes ao período JAN a ABR/2016; oriundos do Contrato 18/</t>
+          <t xml:space="preserve">Despesa com pagamento de serviço de suporte técnico em sistema de informação, conforme NFS-e Nºs 16732 e 16724, referente aos meses de OUT e NOV/2015; oriundo do Contrato 94/2011-SSP, para atender as </t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2021NE0000609</t>
+          <t>2021NE0000612</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>945610.24</v>
+        <v>509.09</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3855,14 +3855,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>DESPESAS COM SERVIÇOS DE HOSPEDAGEM DE SISTEMAS DE SERVIDORES E OUTROS, NFS-e nºs: 16730, 16731, 16738, 16739, 16725, 16726, 16727, 16728, 16729, 16733, 16734, 16735, 16736, 16737 e PROPOSTA Nº 055/20</t>
+          <t>Despesa com execução de sistemas, conforme NFS-e Nº 20207, no valor R$ 509,09, referente ao período SET/2016, para atender necessidades do Sistema de Segurança Pública. Parecer 50/2017-AJUR/SSP.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2021NE0000612</t>
+          <t>2021NE0000609</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>509.09</v>
+        <v>945610.24</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3881,14 +3881,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Despesa com execução de sistemas, conforme NFS-e Nº 20207, no valor R$ 509,09, referente ao período SET/2016, para atender necessidades do Sistema de Segurança Pública. Parecer 50/2017-AJUR/SSP.</t>
+          <t>DESPESAS COM SERVIÇOS DE HOSPEDAGEM DE SISTEMAS DE SERVIDORES E OUTROS, NFS-e nºs: 16730, 16731, 16738, 16739, 16725, 16726, 16727, 16728, 16729, 16733, 16734, 16735, 16736, 16737 e PROPOSTA Nº 055/20</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2021NE0000610</t>
+          <t>2021NE0000613</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>303477.86</v>
+        <v>1747120.16</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3907,14 +3907,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Despesa com pagamento de serviço de suporte técnico em sistema de informação, conforme NFS-e Nºs 16732 e 16724, referente aos meses de OUT e NOV/2015; oriundo do Contrato 94/2011-SSP, para atender as </t>
+          <t>Despesas com serviços de hospedagem de sistemas de servidores e outros; NFS-e 18092 a 18099; 18100 a 18107; 18109 a 18116; 18699 a 18706; referentes ao período JAN a ABR/2016; oriundos do Contrato 18/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2021NE0000611</t>
+          <t>2021NE0000614</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>151738.93</v>
+        <v>436780.04</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>DESPESAS COM SERVIÇOS DE SUPORTE TÉCNICO EM SISTEMAS DE INFORMAÇÃO, NFS-e Nº 17138 VALOR R$ 151.738,93, REFERENTE AO MÊS DE DEZEMBRO/2015, PARA ATENDER NECESSIDADES DO SISTEMA DE SEGURANÇA PUBLICA.</t>
+          <t>Despesa de exercício anterior referente a prestação de serviço de Hospedagem de sistema e suporte técnico em sistema de informação, para atender as necessidades do SSP, NFS-e nº 25802, 25803, 25804, 2</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025NE0000873</t>
+          <t>2025NE0000872</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1666.32</v>
+        <v>2158.37</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025NE0000872</t>
+          <t>2025NE0000873</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2158.37</v>
+        <v>1666.32</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4180,14 +4180,10 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020NE00963</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>18/2016</t>
-        </is>
-      </c>
+          <t>2020NE00962</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
           <t>10/11/2020</t>
@@ -4203,17 +4199,21 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviço de informática, manutenção e suporte a operação, serviço técnico em telecomunicações, fornecimento de circuito de transmissão de dados e disponibilizaçã</t>
+          <t>Anulação total da 2020NE00961, para correção de tipo de empenho.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020NE00963</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>2020NE00961</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>18/2016</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
           <t>10/11/2020</t>
@@ -4236,14 +4236,10 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020NE00961</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>18/2016</t>
-        </is>
-      </c>
+          <t>2020NE00963</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>10/11/2020</t>
@@ -4266,10 +4262,14 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020NE00962</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>2020NE00963</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>18/2016</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>10/11/2020</t>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anulação total da 2020NE00961, para correção de tipo de empenho.</t>
+          <t>Contratação de empresa especializada em serviço de informática, manutenção e suporte a operação, serviço técnico em telecomunicações, fornecimento de circuito de transmissão de dados e disponibilizaçã</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025NE0001607</t>
+          <t>2025NE0001606</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2940.56</v>
+        <v>3808.89</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025NE0001606</t>
+          <t>2025NE0001607</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3808.89</v>
+        <v>2940.56</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2023NE0001134</t>
+          <t>2023NE01134</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4667,14 +4667,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Contratação de empresa para serviço de acesso à internet, acesso a MetroMao, circuito de transmissão de dados, licença de sistema, hospedagem, Firewall, Datawarehouse, suporte técnico, desenvolvimento</t>
+          <t>4º T.A Contrato 048/2021 - Prorrogação de Prazo</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2023NE01134</t>
+          <t>2023NE0001134</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>4º T.A Contrato 048/2021 - Prorrogação de Prazo</t>
+          <t>Contratação de empresa para serviço de acesso à internet, acesso a MetroMao, circuito de transmissão de dados, licença de sistema, hospedagem, Firewall, Datawarehouse, suporte técnico, desenvolvimento</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025NE0001854</t>
+          <t>2025NE0001853</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2940.56</v>
+        <v>3808.89</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025NE0001853</t>
+          <t>2025NE0001854</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3808.89</v>
+        <v>2940.56</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2014NE00768</t>
+          <t>2014NE00750</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>910.76</v>
+        <v>23983.48</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2014NE00750</t>
+          <t>2014NE00768</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>23983.48</v>
+        <v>910.76</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2019NE01619</t>
+          <t>2019NE01591</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4963,14 +4963,14 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Contratação de emp. especializada em serv de informática, manutenção e suporte a operação,serviço téc. em telecomunicações, fornecimento de circuito de trans. de dados e disponibilização de links pont</t>
+          <t>Contratação de emp especializada em serviço de informática, manutenção e suporte a operação, serviço téc em telecomunicações, fornecimento de circuito de trans de dados e disponibilização de links pon</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2019NE01591</t>
+          <t>2019NE01619</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4993,14 +4993,14 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Contratação de emp especializada em serviço de informática, manutenção e suporte a operação, serviço téc em telecomunicações, fornecimento de circuito de trans de dados e disponibilização de links pon</t>
+          <t>Contratação de emp. especializada em serv de informática, manutenção e suporte a operação,serviço téc. em telecomunicações, fornecimento de circuito de trans. de dados e disponibilização de links pont</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2018NE00217</t>
+          <t>2018NE00218</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>32595</v>
+        <v>1790798.16</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5023,14 +5023,14 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviço especializado em informática, com manutenção e suporte a operação, serviço técnico em telecomunicações e fornecimento de circuito de transmissão de dado</t>
+          <t>Contratação de empresa para prestar serv de especializado em informática, manutenção e suporte a operação, serv técnico em telecomunicações, com fornecimento de circuito de transmissão de dados de lin</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2018NE00218</t>
+          <t>2018NE00217</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1790798.16</v>
+        <v>32595</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestar serv de especializado em informática, manutenção e suporte a operação, serv técnico em telecomunicações, com fornecimento de circuito de transmissão de dados de lin</t>
+          <t>Contratação de empresa especializada em serviço especializado em informática, com manutenção e suporte a operação, serviço técnico em telecomunicações e fornecimento de circuito de transmissão de dado</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5090,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026NE0000007</t>
+          <t>2026NE0000002</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>22/2025</t>
+          <t>18/2025</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8102107.04</v>
+        <v>39524</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5113,19 +5113,19 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço vinculado ao Sistema Único Integrado de Segurança Pública, para atender às necessidades do Sistema de Segurança Pública do Estado do Amazon</t>
+          <t>Contratação de empresa especializada em serviço de acesso ao legado do Sistema Sisp, ara atender as necessidades da Secretaria de Estado de Segurança Pública do Amazonas.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026NE0000006</t>
+          <t>2026NE0000008</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>22/2025</t>
+          <t>19/2025</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5948895</v>
+        <v>15235.56</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço vinculado ao Sistema Único Integrado de Segurança Pública, para atender às necessidades do Sistema de Segurança Pública do Estado do Amazon</t>
+          <t>Contratação de empresa especializada na prestação de serviço de fornecimento de circuito de transmissão de dados, licença de uso dos Sistemas Gerweb e Intrega, para atender as necessidades da Secretar</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026NE0000008</t>
+          <t>2026NE0000006</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>19/2025</t>
+          <t>22/2025</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>15235.56</v>
+        <v>5948895</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5203,19 +5203,19 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de fornecimento de circuito de transmissão de dados, licença de uso dos Sistemas Gerweb e Intrega, para atender as necessidades da Secretar</t>
+          <t>Contratação de empresa especializada na prestação de serviço vinculado ao Sistema Único Integrado de Segurança Pública, para atender às necessidades do Sistema de Segurança Pública do Estado do Amazon</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026NE0000002</t>
+          <t>2026NE0000007</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>18/2025</t>
+          <t>22/2025</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>39524</v>
+        <v>8102107.04</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviço de acesso ao legado do Sistema Sisp, ara atender as necessidades da Secretaria de Estado de Segurança Pública do Amazonas.</t>
+          <t>Contratação de empresa especializada na prestação de serviço vinculado ao Sistema Único Integrado de Segurança Pública, para atender às necessidades do Sistema de Segurança Pública do Estado do Amazon</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2015NE00021</t>
+          <t>2015NE00023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>72/2011</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>7177.29</v>
+        <v>41899.71</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5293,19 +5293,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Cobertura financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2015NE00070</t>
+          <t>2015NE00071</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>28/2011</t>
+          <t>83/2014</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>17334.18</v>
+        <v>26709.6</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5323,19 +5323,19 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Despesa com 3º TA ao Contrato nº 028/2011-SSP, serviço de geoprocessamento do Programa Ronda no Bairro.</t>
+          <t>Despesa com Contrato nº83/2014-SSP, serviço de Hospedagem do Sistema INFOPOL.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2015NE00071</t>
+          <t>2015NE00070</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>83/2014</t>
+          <t>28/2011</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>26709.6</v>
+        <v>17334.18</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5353,19 +5353,19 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Despesa com Contrato nº83/2014-SSP, serviço de Hospedagem do Sistema INFOPOL.</t>
+          <t>Despesa com 3º TA ao Contrato nº 028/2011-SSP, serviço de geoprocessamento do Programa Ronda no Bairro.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2015NE00023</t>
+          <t>2015NE00021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>72/2011</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>41899.71</v>
+        <v>7177.29</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2019NE01288</t>
+          <t>2019NE01289</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>24592.1</v>
+        <v>31736.85</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5439,14 +5439,14 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Anulação parcial do saldo da 2019NE00078, conforme o faturamento do período de vigência do contrato, no valor de R$ 24.592,10.</t>
+          <t>Anulação parcial do saldo da 2019NE00365, conforme o faturamento do período de vigência do contrato, no valor de R$ 31.736,85.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2019NE01289</t>
+          <t>2019NE01288</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>31736.85</v>
+        <v>24592.1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5465,14 +5465,14 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Anulação parcial do saldo da 2019NE00365, conforme o faturamento do período de vigência do contrato, no valor de R$ 31.736,85.</t>
+          <t>Anulação parcial do saldo da 2019NE00078, conforme o faturamento do período de vigência do contrato, no valor de R$ 24.592,10.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2022NE0001548</t>
+          <t>2022NE0001547</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>28939.98</v>
+        <v>37547.26</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA 2022NE0001192 NO VALOR DE R$ 28.939,98, CONFORME DESCRITO NO MEMO CIRC Nº 058/2022-GSE/SSP-AM-FOLHA 19, EM RAZÃO DOS FATURAMENTOS NOS MESES DE AGOSTO E SETEMBRO DE 2022.</t>
+          <t>ANULAÇÃO DO SALDO DA 2022NE0000066 NO VALOR DE R$ 37.547,26, CONFORME DESCRITO NO MEMO CIRC Nº 058/2022-GSE/SSP-AM-FOLHA 19, EM RAZÃO DOS FATURAMENTOS NO MÊS DE AGOSTO DE 2022.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2022NE0001547</t>
+          <t>2022NE0001548</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>37547.26</v>
+        <v>28939.98</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA 2022NE0000066 NO VALOR DE R$ 37.547,26, CONFORME DESCRITO NO MEMO CIRC Nº 058/2022-GSE/SSP-AM-FOLHA 19, EM RAZÃO DOS FATURAMENTOS NO MÊS DE AGOSTO DE 2022.</t>
+          <t>ANULAÇÃO DO SALDO DA 2022NE0001192 NO VALOR DE R$ 28.939,98, CONFORME DESCRITO NO MEMO CIRC Nº 058/2022-GSE/SSP-AM-FOLHA 19, EM RAZÃO DOS FATURAMENTOS NOS MESES DE AGOSTO E SETEMBRO DE 2022.</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025NE0001081</t>
+          <t>2025NE0001082</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>7617.78</v>
+        <v>5881.12</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025NE0001082</t>
+          <t>2025NE0001081</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5881.12</v>
+        <v>7617.78</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5760,14 +5760,10 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2022NE0000056</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>48/2021</t>
-        </is>
-      </c>
+          <t>2022NE0000061</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>03/01/2022</t>
@@ -5783,17 +5779,21 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso à internet,desenvolvimento de sistema de informação,serviço de transmissão de dados, serviços de informática,hospedagem de sistema de informa</t>
+          <t>Anulação total da 2022NE0000056, no valor de R$ 2.143.809,04 para ajuste do cronograma.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2022NE0000061</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
+          <t>2022NE0000056</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>48/2021</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr">
         <is>
           <t>03/01/2022</t>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Anulação total da 2022NE0000056, no valor de R$ 2.143.809,04 para ajuste do cronograma.</t>
+          <t>Contratação de empresa especializada em serviços de acesso à internet,desenvolvimento de sistema de informação,serviço de transmissão de dados, serviços de informática,hospedagem de sistema de informa</t>
         </is>
       </c>
     </row>
@@ -6236,12 +6236,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2014NE00035</t>
+          <t>2014NE00020</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>68/2012</t>
+          <t>67/2012</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>4388613.31</v>
+        <v>1634417.25</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6259,19 +6259,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Contrato No. 68/2012 - Links (59), Internet e Hospedagem.</t>
+          <t>Contrato No. 67/2012 - Hospedagem do SISP</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2014NE00033</t>
+          <t>2014NE00059</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>94/2011</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>7546.88</v>
+        <v>3291563.56</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6289,19 +6289,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Contrato No. 12/2012 - Hospedagem do Sistema de Gerenciamento de Denúncias</t>
+          <t>Contrato No. 94/2011 - Manutenção de Solução Tecnológica do CIOPS</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2014NE00042</t>
+          <t>2014NE00030</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>72/2011</t>
+          <t>28/2011</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>122482.92</v>
+        <v>37457.35</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6319,19 +6319,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Contrato No. 72/2011 - Serviços Eventuais de Informatica SSP/SEAI</t>
+          <t>Contrato No. 28/2011 - Locação de Equipamentos Ronda nos Bairros</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2014NE00030</t>
+          <t>2014NE00042</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>28/2011</t>
+          <t>72/2011</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>37457.35</v>
+        <v>122482.92</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6349,19 +6349,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Contrato No. 28/2011 - Locação de Equipamentos Ronda nos Bairros</t>
+          <t>Contrato No. 72/2011 - Serviços Eventuais de Informatica SSP/SEAI</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2014NE00059</t>
+          <t>2014NE00033</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>94/2011</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>3291563.56</v>
+        <v>7546.88</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6379,19 +6379,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Contrato No. 94/2011 - Manutenção de Solução Tecnológica do CIOPS</t>
+          <t>Contrato No. 12/2012 - Hospedagem do Sistema de Gerenciamento de Denúncias</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2014NE00020</t>
+          <t>2014NE00035</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>67/2012</t>
+          <t>68/2012</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1634417.25</v>
+        <v>4388613.31</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Contrato No. 67/2012 - Hospedagem do SISP</t>
+          <t>Contrato No. 68/2012 - Links (59), Internet e Hospedagem.</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6446,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2015NE00875</t>
+          <t>2015NE00878</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>72/2011</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>41899.71</v>
+        <v>797.98</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6469,19 +6469,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00023, REFERENTE AO 3º TERMO ADITIVO AO CONTRATO Nº 072/2011-SSP, COM VIGÊNCIA ATÉ OUTUBRO/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00342, REFERENTE AO 2º TERMO ADITIVO AO CONTRATO Nº 012/2012-SSP, COM VIGÊNCIA ATÉ ABRIL/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº 0</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2015NE00876</t>
+          <t>2015NE00877</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>28/2011</t>
+          <t>83/2014</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>17334.18</v>
+        <v>26709.6</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6499,19 +6499,19 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00070, REFERENTE AO 3º TERMO ADITIVO AO CONTRATO Nº 028/2011-SSP, COM VIGÊNCIA ATÉ AGOSTO/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº </t>
+          <t xml:space="preserve">ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00071, REFERENTE AO CONTRATO Nº 083/2014-SSP, COM VIGÊNCIA ATÉ SETEMBR/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº 0442/2015-CEAG, DE </t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2015NE00877</t>
+          <t>2015NE00876</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>83/2014</t>
+          <t>28/2011</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>26709.6</v>
+        <v>17334.18</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6529,19 +6529,19 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00071, REFERENTE AO CONTRATO Nº 083/2014-SSP, COM VIGÊNCIA ATÉ SETEMBR/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº 0442/2015-CEAG, DE </t>
+          <t xml:space="preserve">ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00070, REFERENTE AO 3º TERMO ADITIVO AO CONTRATO Nº 028/2011-SSP, COM VIGÊNCIA ATÉ AGOSTO/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº </t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2015NE00878</t>
+          <t>2015NE00875</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>72/2011</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>797.98</v>
+        <v>41899.71</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00342, REFERENTE AO 2º TERMO ADITIVO AO CONTRATO Nº 012/2012-SSP, COM VIGÊNCIA ATÉ ABRIL/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº 0</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº 2015NE00023, REFERENTE AO 3º TERMO ADITIVO AO CONTRATO Nº 072/2011-SSP, COM VIGÊNCIA ATÉ OUTUBRO/2015, PROCEDIMENTO PARA ATENDER SOLICITAÇÃO CONTIDA NO OFÍCIO Nº</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2019NE00798</t>
+          <t>2019NE00799</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>50036.2</v>
+        <v>1258.05</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviço de informática, manutenção e suporte a operação, serviço técnico em telecomunicações, fornecimento de circuito de transmissão de dados e disponibilizaçã</t>
+          <t xml:space="preserve">Contratação de empresa especializada para atender o presente Termo Aditivo cujo objeto é inclusão de oito links ponto a ponto para as unidades SEAI, Batalhão de Choque da PM, Perícia Criminal, e mais </t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2019NE00799</t>
+          <t>2019NE00798</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1258.05</v>
+        <v>50036.2</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6679,14 +6679,14 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada para atender o presente Termo Aditivo cujo objeto é inclusão de oito links ponto a ponto para as unidades SEAI, Batalhão de Choque da PM, Perícia Criminal, e mais </t>
+          <t>Contratação de empresa especializada em serviço de informática, manutenção e suporte a operação, serviço técnico em telecomunicações, fornecimento de circuito de transmissão de dados e disponibilizaçã</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2019NE00365</t>
+          <t>2019NE00376</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>37741.65</v>
+        <v>1501086.12</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6709,14 +6709,14 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada para atender o presente Termo Aditivo cujo objeto é inclusão de oito links ponto a ponto para as unidades SEAI, Batalhão de Choque da PM, Perícia Criminal, e mais </t>
+          <t>Contratação de empresa especializada em serviço de informática, manutenção e suporte a operação, serviço técnico em telecomunicações, fornecimento de circuito de transmissão de dados e disponibilizaçã</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2019NE00376</t>
+          <t>2019NE00365</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1501086.12</v>
+        <v>37741.65</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviço de informática, manutenção e suporte a operação, serviço técnico em telecomunicações, fornecimento de circuito de transmissão de dados e disponibilizaçã</t>
+          <t xml:space="preserve">Contratação de empresa especializada para atender o presente Termo Aditivo cujo objeto é inclusão de oito links ponto a ponto para as unidades SEAI, Batalhão de Choque da PM, Perícia Criminal, e mais </t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2018NE00207</t>
+          <t>2018NE00208</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1790798.16</v>
+        <v>32595</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6825,14 +6825,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Anulação parcial da Nota de Empenho 2018NE00092 para correção de natureza de despesa conforme orientação repassada pelo Órgão Centralizador.</t>
+          <t>Anulação parcial da Nota de Empenho 2018NE00111 para correção de natureza de despesa conforme orientação repassada pelo Órgão Centralizador.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2018NE00208</t>
+          <t>2018NE00207</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>32595</v>
+        <v>1790798.16</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Anulação parcial da Nota de Empenho 2018NE00111 para correção de natureza de despesa conforme orientação repassada pelo Órgão Centralizador.</t>
+          <t>Anulação parcial da Nota de Empenho 2018NE00092 para correção de natureza de despesa conforme orientação repassada pelo Órgão Centralizador.</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SSP/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SSP/dossie.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
